--- a/AnalisisFinanciero/data/890903939_2024-12-31_Notas_Cuentas_comerciales_por_pagar_otras_cuentas_por_pagar_y_otros_pasivos_financieros_traduccion.xlsx
+++ b/AnalisisFinanciero/data/890903939_2024-12-31_Notas_Cuentas_comerciales_por_pagar_otras_cuentas_por_pagar_y_otros_pasivos_financieros_traduccion.xlsx
@@ -1,15 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99ECFD01-F6CC-4A93-8216-BBFD377B6B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Hoja1" state="visible" r:id="rId4"/>
+    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -106,33 +128,34 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
       <name val="Microsoft Sans Serif"/>
+      <sz val="9.00"/>
+      <family val="2"/>
     </font>
     <font>
-      <color indexed="8"/>
+      <name val="Calibri"/>
+      <sz val="11.00"/>
+      <color rgb="FF000000"/>
       <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Microsoft Sans Serif"/>
+      <sz val="9.00"/>
       <b/>
-      <sz val="9"/>
-      <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,25 +165,137 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="darkDown">
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -169,142 +304,452 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
       <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="2" applyFont="1" borderId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" borderId="9" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="9" applyFill="1" borderId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="12" applyFill="1" borderId="13" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="13" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="14" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="3" applyFont="1" fillId="15" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="16" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="17" applyFill="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="18" applyFill="1" borderId="19" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="19" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="20" applyFill="1" borderId="21" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="21" applyFill="1" borderId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf fontId="2" applyFont="1" fillId="22" applyFill="1" borderId="23" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="1" applyFont="1" fillId="23" applyFill="1" borderId="24" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="21" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="20" applyFill="1" borderId="21" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="12" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="11" applyFill="1" borderId="12" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="4" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="11" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="10" applyFill="1" borderId="11" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="20" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="19" applyFill="1" borderId="20" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="15" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="14" applyFill="1" borderId="15" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="1" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="7" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="7" applyFill="1" borderId="7" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="center" wrapText="1"/>
+    </xf>
+    <xf xfId="14" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="13" applyFill="1" borderId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="13" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="12" applyFill="1" borderId="13" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="8" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="8" applyFill="1" borderId="8" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="23" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="22" applyFill="1" borderId="23" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="10" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="9" applyFill="1" borderId="10" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="24" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="23" applyFill="1" borderId="24" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="18" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="17" applyFill="1" borderId="18" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="6" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="6" applyFill="1" borderId="6" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="22" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="21" applyFill="1" borderId="22" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="9" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="9" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="17" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="16" applyFill="1" borderId="17" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="2" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="16" quotePrefix="0" pivotButton="0" fontId="3" applyFont="1" fillId="15" applyFill="1" borderId="16" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="5" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="5" applyFill="1" borderId="5" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="19" quotePrefix="0" pivotButton="0" fontId="1" applyFont="1" fillId="18" applyFill="1" borderId="19" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="3" quotePrefix="0" pivotButton="0" fontId="2" applyFont="1" borderId="3" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -320,7 +765,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -336,7 +781,7 @@
         <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
         <a:srgbClr val="ED7D31"/>
@@ -348,7 +793,7 @@
         <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
         <a:srgbClr val="70AD47"/>
@@ -395,23 +840,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -447,23 +875,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -501,15 +912,15 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
@@ -570,32 +981,32 @@
         </a:solidFill>
         <a:solidFill>
           <a:schemeClr val="phClr">
+            <a:satMod val="170000"/>
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:satMod val="120000"/>
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -615,16 +1026,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25" defaultColWidth="9.140625"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.00" customHeight="1" defaultColWidth="9.20"/>
   <cols>
-    <col min="1" max="2" width="2.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50" customWidth="1"/>
-    <col min="4" max="12" width="15" customWidth="1"/>
+    <col min="1" max="2" width="2.70" customWidth="1" hidden="0"/>
+    <col min="3" max="3" width="50.04" customWidth="1" hidden="0"/>
+    <col min="4" max="12" width="14.96" customWidth="1" hidden="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.00" customHeight="true">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -637,7 +1049,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="2" ht="15.00" customHeight="true">
       <c r="D2" s="4" t="s">
         <v>1</v>
       </c>
@@ -652,7 +1064,7 @@
       <c r="K2" s="5"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" ht="63.75" customHeight="1" spans="4:12" x14ac:dyDescent="0.25">
+    <row r="3" ht="63.75" customHeight="true">
       <c r="D3" s="7" t="s">
         <v>3</v>
       </c>
@@ -681,7 +1093,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" ht="29.25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" ht="29.25" customHeight="true">
       <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
@@ -697,7 +1109,7 @@
       <c r="K4" s="12"/>
       <c r="L4" s="12"/>
     </row>
-    <row r="5" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" ht="27.75" customHeight="true">
       <c r="A5" s="13"/>
       <c r="B5" s="14" t="s">
         <v>13</v>
@@ -713,7 +1125,7 @@
       <c r="K5" s="12"/>
       <c r="L5" s="12"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" ht="15.00" customHeight="true">
       <c r="A6" s="13"/>
       <c r="B6" s="16"/>
       <c r="C6" s="17" t="s">
@@ -737,7 +1149,7 @@
       <c r="K6" s="18"/>
       <c r="L6" s="18"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" ht="15.00" customHeight="true">
       <c r="A7" s="13"/>
       <c r="B7" s="16"/>
       <c r="C7" s="19" t="s">
@@ -757,7 +1169,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="20"/>
     </row>
-    <row r="8" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" ht="25.50" customHeight="true">
       <c r="A8" s="13"/>
       <c r="B8" s="16"/>
       <c r="C8" s="21" t="s">
@@ -781,7 +1193,7 @@
       <c r="K8" s="18"/>
       <c r="L8" s="18"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" ht="15.00" customHeight="true">
       <c r="A9" s="13"/>
       <c r="B9" s="16"/>
       <c r="C9" s="19" t="s">
@@ -803,7 +1215,7 @@
       <c r="K9" s="20"/>
       <c r="L9" s="20"/>
     </row>
-    <row r="10" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" ht="25.50" customHeight="true">
       <c r="A10" s="13"/>
       <c r="B10" s="16"/>
       <c r="C10" s="21" t="s">
@@ -827,7 +1239,7 @@
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" ht="15.00" customHeight="true">
       <c r="A11" s="13"/>
       <c r="B11" s="16"/>
       <c r="C11" s="19" t="s">
@@ -843,7 +1255,7 @@
       <c r="K11" s="20"/>
       <c r="L11" s="20"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" ht="15.00" customHeight="true">
       <c r="A12" s="13"/>
       <c r="B12" s="22"/>
       <c r="C12" s="17" t="s">
@@ -859,7 +1271,7 @@
       <c r="K12" s="18"/>
       <c r="L12" s="18"/>
     </row>
-    <row r="13" ht="27.95" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" ht="27.75" customHeight="true">
       <c r="A13" s="13"/>
       <c r="B13" s="14" t="s">
         <v>21</v>
@@ -875,7 +1287,7 @@
       <c r="K13" s="12"/>
       <c r="L13" s="12"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" ht="15.00" customHeight="true">
       <c r="A14" s="13"/>
       <c r="B14" s="16"/>
       <c r="C14" s="17" t="s">
@@ -891,7 +1303,7 @@
       <c r="K14" s="18"/>
       <c r="L14" s="18"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" ht="15.00" customHeight="true">
       <c r="A15" s="13"/>
       <c r="B15" s="16"/>
       <c r="C15" s="19" t="s">
@@ -907,7 +1319,7 @@
       <c r="K15" s="20"/>
       <c r="L15" s="20"/>
     </row>
-    <row r="16" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" ht="25.50" customHeight="true">
       <c r="A16" s="13"/>
       <c r="B16" s="16"/>
       <c r="C16" s="21" t="s">
@@ -923,7 +1335,7 @@
       <c r="K16" s="18"/>
       <c r="L16" s="18"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" ht="15.00" customHeight="true">
       <c r="A17" s="13"/>
       <c r="B17" s="16"/>
       <c r="C17" s="19" t="s">
@@ -945,7 +1357,7 @@
       <c r="K17" s="20"/>
       <c r="L17" s="20"/>
     </row>
-    <row r="18" ht="25.5" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" ht="25.50" customHeight="true">
       <c r="A18" s="13"/>
       <c r="B18" s="16"/>
       <c r="C18" s="21" t="s">
@@ -967,7 +1379,7 @@
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" ht="15.00" customHeight="true">
       <c r="A19" s="13"/>
       <c r="B19" s="16"/>
       <c r="C19" s="19" t="s">
@@ -983,7 +1395,7 @@
       <c r="K19" s="20"/>
       <c r="L19" s="20"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" ht="15.00" customHeight="true">
       <c r="A20" s="23"/>
       <c r="B20" s="22"/>
       <c r="C20" s="17" t="s">
@@ -1008,6 +1420,9 @@
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B13:C13"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="0" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.25" footer="0.25"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="100"/>
+  <headerFooter alignWithMargins="1"/>
 </worksheet>
 </file>